--- a/notification_configs/01_daily_status_reminders.xlsx
+++ b/notification_configs/01_daily_status_reminders.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyStatusReminders" displayName="DailyStatusReminders" ref="A1:U14" headerRowCount="1">
-  <autoFilter ref="A1:U14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyStatusReminders" displayName="DailyStatusReminders" ref="A1:U7" headerRowCount="1">
+  <autoFilter ref="A1:U7"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
@@ -443,15 +443,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="29" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -579,35 +579,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VENDOR_OT1_20250910</t>
+          <t>VENDOR_01111_20250911</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ot1@vendor.com</t>
+          <t>thunderblunder018@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Gopal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OT1</t>
+          <t>01111</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WCS/MSE7</t>
+          <t>DEV</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vendor Company</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>MEdiatek</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MTK34710</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
@@ -636,12 +640,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - Test</t>
+          <t>Please submit your daily attendance status - Gopal</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>vendor_ot1</t>
+          <t>vendor_01111</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -661,47 +665,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VENDOR_OT2_20250910</t>
+          <t>VENDOR_EMP001_20250911</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ot2@vendor.com</t>
+          <t>john.vendor@company.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>abc2</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OT2</t>
+          <t>EMP001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WCS/MSE7</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vendor Company</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>TechCorp Solutions</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>3</v>
       </c>
@@ -730,12 +738,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - abc2</t>
+          <t>Please submit your daily attendance status - John Smith</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>vendor_ot2</t>
+          <t>vendor_emp001</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -755,47 +763,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VENDOR_OT3_20250910</t>
+          <t>VENDOR_EMP002_20250911</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ot3@vendor.com</t>
+          <t>jane.vendor@company.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>abc3</t>
+          <t>Jane Wilson</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OT3</t>
+          <t>EMP002</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WCS/MSE8</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vendor Company</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>TechCorp Solutions</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -824,12 +836,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - abc3</t>
+          <t>Please submit your daily attendance status - Jane Wilson</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>vendor_ot3</t>
+          <t>vendor_emp002</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -849,45 +861,49 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VENDOR_V001_20250910</t>
+          <t>VENDOR_EMP003_20250911</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chandresh.kerkar1@gmail.com</t>
+          <t>mike.vendor@company.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chandresh Kerkar</t>
+          <t>Mike Rodriguez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>V001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PandaPaths</t>
+          <t>InfraCorp Ltd</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -918,12 +934,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - Chandresh Kerkar</t>
+          <t>Please submit your daily attendance status - Mike Rodriguez</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>vendor_v001</t>
+          <t>vendor_emp003</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -943,49 +959,49 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VENDOR_VND002_20250910</t>
+          <t>VENDOR_EMP004_20250911</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jane.smith@vendor1.com</t>
+          <t>sarah.vendor@company.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jane Smith</t>
+          <t>Sarah Parker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VND002</t>
+          <t>EMP004</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MTB_WCS_MSE7_MS1</t>
+          <t>Quality Assurance</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABC Solutions</t>
+          <t>QualityCorp Inc</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1016,12 +1032,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - Jane Smith</t>
+          <t>Please submit your daily attendance status - Sarah Parker</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>vendor_vnd002</t>
+          <t>vendor_emp004</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1041,44 +1057,44 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VENDOR_VND003_20250910</t>
+          <t>VENDOR_EMP005_20250911</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>robert.wilson@vendor2.com</t>
+          <t>david.vendor@company.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Robert Wilson</t>
+          <t>David Kim</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VND003</t>
+          <t>EMP005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MTB_WCS_MSE7_MS1</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>XYZ Technologies</t>
+          <t>TechCorp Solutions</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1114,12 +1130,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - Robert Wilson</t>
+          <t>Please submit your daily attendance status - David Kim</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>vendor_vnd003</t>
+          <t>vendor_emp005</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1139,698 +1155,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>VENDOR_VND004_20250910</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>lisa.brown@vendor2.com</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Lisa Brown</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VND004</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MTB_WCS_MSE7_MS2</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>XYZ Technologies</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>M002</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - Lisa Brown</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>vendor_vnd004</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VENDOR_VND005_20250910</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>david.lee@vendor3.com</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>David Lee</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VND005</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MTB_WCS_MSE7_MS2</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tech Partners</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>M002</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - David Lee</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>vendor_vnd005</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>VENDOR_VND006_20250910</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>maria.garcia@vendor3.com</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Maria Garcia</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VND006</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MTB_WCS_MSE7_MS2</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tech Partners</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>M002</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - Maria Garcia</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>vendor_vnd006</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>VENDOR_VND007_20250910</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>james.miller@vendor4.com</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>James Miller</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>VND007</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MTB_WCS_MSE7_MS3</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Digital Innovations</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>M003</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - James Miller</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>vendor_vnd007</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>VENDOR_VND008_20250910</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>anna.taylor@vendor4.com</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Anna Taylor</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VND008</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MTB_WCS_MSE7_MS3</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Digital Innovations</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>M003</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - Anna Taylor</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>vendor_vnd008</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>VENDOR_VND009_20250910</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>chris.anderson@vendor5.com</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Chris Anderson</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VND009</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MTB_WCS_MSE7_MS3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Smart Systems</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>M003</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - Chris Anderson</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>vendor_vnd009</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>VENDOR_VND010_20250910</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>sophie.martin@vendor5.com</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sophie Martin</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VND010</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MTB_WCS_MSE7_MS1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Smart Systems</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>M001</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - Sophie Martin</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>vendor_vnd010</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>

--- a/notification_configs/01_daily_status_reminders.xlsx
+++ b/notification_configs/01_daily_status_reminders.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>

--- a/notification_configs/01_daily_status_reminders.xlsx
+++ b/notification_configs/01_daily_status_reminders.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyStatusReminders" displayName="DailyStatusReminders" ref="A1:U7" headerRowCount="1">
-  <autoFilter ref="A1:U7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyStatusReminders" displayName="DailyStatusReminders" ref="A1:U10" headerRowCount="1">
+  <autoFilter ref="A1:U10"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,289 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VENDOR_OT1_20250911</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ot1@vendor.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abc1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OT1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WCS/MSE7</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vendor Company</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Please submit your daily attendance status - abc1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>vendor_ot1</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2025-09-11 19:08:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VENDOR_OT2_20250911</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ot2@vendor.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abc2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OT2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WCS/MSE7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vendor Company</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Please submit your daily attendance status - abc2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>vendor_ot2</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2025-09-11 19:08:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VENDOR_OT3_20250911</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ot3@vendor.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abc3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OT3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>WCS/MSE8</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vendor Company</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Please submit your daily attendance status - abc3</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>vendor_ot3</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>

--- a/notification_configs/01_daily_status_reminders.xlsx
+++ b/notification_configs/01_daily_status_reminders.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyStatusReminders" displayName="DailyStatusReminders" ref="A1:U10" headerRowCount="1">
-  <autoFilter ref="A1:U10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyStatusReminders" displayName="DailyStatusReminders" ref="A1:U6" headerRowCount="1">
+  <autoFilter ref="A1:U6"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
@@ -443,11 +443,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -579,37 +579,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VENDOR_01111_20250911</t>
+          <t>VENDOR_EMP001_20250911</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>thunderblunder018@gmail.com</t>
+          <t>john.vendor@company.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gopal</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>01111</t>
+          <t>EMP001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DEV</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MEdiatek</t>
+          <t>TechCorp Solutions</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MTK34710</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -640,12 +640,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - Gopal</t>
+          <t>Please submit your daily attendance status - John Smith</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>vendor_01111</t>
+          <t>vendor_emp001</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -670,29 +670,29 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VENDOR_EMP001_20250911</t>
+          <t>VENDOR_EMP002_20250911</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>john.vendor@company.com</t>
+          <t>jane.vendor@company.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Jane Wilson</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EMP001</t>
+          <t>EMP002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - John Smith</t>
+          <t>Please submit your daily attendance status - Jane Wilson</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>vendor_emp001</t>
+          <t>vendor_emp002</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -768,44 +768,44 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VENDOR_EMP002_20250911</t>
+          <t>VENDOR_EMP003_20250911</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jane.vendor@company.com</t>
+          <t>mike.vendor@company.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jane Wilson</t>
+          <t>Mike Rodriguez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EMP002</t>
+          <t>EMP003</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TechCorp Solutions</t>
+          <t>InfraCorp Ltd</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -836,12 +836,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - Jane Wilson</t>
+          <t>Please submit your daily attendance status - Mike Rodriguez</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>vendor_emp002</t>
+          <t>vendor_emp003</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -866,44 +866,44 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VENDOR_EMP003_20250911</t>
+          <t>VENDOR_EMP004_20250911</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mike.vendor@company.com</t>
+          <t>sarah.vendor@company.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mike Rodriguez</t>
+          <t>Sarah Parker</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EMP003</t>
+          <t>EMP004</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Quality Assurance</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>InfraCorp Ltd</t>
+          <t>QualityCorp Inc</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -934,12 +934,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - Mike Rodriguez</t>
+          <t>Please submit your daily attendance status - Sarah Parker</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>vendor_emp003</t>
+          <t>vendor_emp004</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -964,44 +964,44 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VENDOR_EMP004_20250911</t>
+          <t>VENDOR_EMP005_20250911</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sarah.vendor@company.com</t>
+          <t>david.vendor@company.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sarah Parker</t>
+          <t>David Kim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EMP004</t>
+          <t>EMP005</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Quality Assurance</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>QualityCorp Inc</t>
+          <t>TechCorp Solutions</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Please submit your daily attendance status - Sarah Parker</t>
+          <t>Please submit your daily attendance status - David Kim</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>vendor_emp004</t>
+          <t>vendor_emp005</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1062,387 +1062,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>VENDOR_EMP005_20250911</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>david.vendor@company.com</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>David Kim</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>EMP005</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TechCorp Solutions</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>M001</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - David Kim</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>vendor_emp005</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>2025-09-11 19:08:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>VENDOR_OT1_20250911</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ot1@vendor.com</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>abc1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>OT1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>WCS/MSE7</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vendor Company</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - abc1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>vendor_ot1</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>2025-09-11 19:08:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VENDOR_OT2_20250911</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ot2@vendor.com</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>abc2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OT2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>WCS/MSE7</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vendor Company</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - abc2</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>vendor_ot2</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>2025-09-11 19:08:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>VENDOR_OT3_20250911</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ot3@vendor.com</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>abc3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>OT3</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>WCS/MSE8</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Vendor Company</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Please submit your daily attendance status - abc3</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>vendor_ot3</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>

--- a/notification_configs/01_daily_status_reminders.xlsx
+++ b/notification_configs/01_daily_status_reminders.xlsx
@@ -125,9 +125,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyStatusReminders" displayName="DailyStatusReminders" ref="A1:U6" headerRowCount="1">
-  <autoFilter ref="A1:U6"/>
-  <tableColumns count="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyStatusReminders" displayName="DailyStatusReminders" ref="A1:Y6" headerRowCount="1">
+  <autoFilter ref="A1:Y6"/>
+  <tableColumns count="25">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
     <tableColumn id="3" name="Vendor_Name"/>
@@ -149,6 +149,10 @@
     <tableColumn id="19" name="Active"/>
     <tableColumn id="20" name="Created_Date"/>
     <tableColumn id="21" name="Last_Updated"/>
+    <tableColumn id="22" name="Submission_Status"/>
+    <tableColumn id="23" name="Reminder_Status"/>
+    <tableColumn id="24" name="Send_Notification"/>
+    <tableColumn id="25" name="Update_Source"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -443,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -467,6 +471,10 @@
     <col width="8" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,6 +583,26 @@
           <t>Last_Updated</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Submission_Status</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Reminder_Status</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Send_Notification</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Update_Source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -648,6 +676,9 @@
           <t>vendor_emp001</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v/>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -670,7 +701,27 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-09-11 22:16:31</t>
+          <t>2025-09-12 02:06:45</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SUBMITTED</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>REALTIME_SUBMISSION</t>
         </is>
       </c>
     </row>
@@ -746,6 +797,9 @@
           <t>vendor_emp002</t>
         </is>
       </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -770,6 +824,18 @@
         <is>
           <t>2025-09-11 22:16:31</t>
         </is>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -844,6 +910,9 @@
           <t>vendor_emp003</t>
         </is>
       </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -868,6 +937,18 @@
         <is>
           <t>2025-09-11 22:16:31</t>
         </is>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -942,6 +1023,9 @@
           <t>vendor_emp004</t>
         </is>
       </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -966,6 +1050,18 @@
         <is>
           <t>2025-09-11 22:16:31</t>
         </is>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1040,6 +1136,9 @@
           <t>vendor_emp005</t>
         </is>
       </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -1064,6 +1163,18 @@
         <is>
           <t>2025-09-11 22:16:31</t>
         </is>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
